--- a/C_et_T/C_et_T_files/Data circuits.xlsx
+++ b/C_et_T/C_et_T_files/Data circuits.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laurent\Dropbox\PERSO - Laurent\INFORMATIQUE\PYTHON\Projet Cursor - Circuit et trajectoires\Base Circuits\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gauth\Dropbox\PERSO - Laurent\INFORMATIQUE\PYTHON\02 - Projet Cursor - Kart simulator\C_et_T\C_et_T_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{767C7CF6-E151-4BAC-9642-25F425DD5521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F0E909C-A625-4A25-89C0-4B58C4BA8BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30EA3A41-EFE0-40BE-84D2-A94FAEB63A11}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{30EA3A41-EFE0-40BE-84D2-A94FAEB63A11}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>44.7553638459408, -0.24425389677166484</t>
   </si>
@@ -55,6 +55,15 @@
   </si>
   <si>
     <t>Je trouve 827M, correct, 3%</t>
+  </si>
+  <si>
+    <t>Sougy</t>
+  </si>
+  <si>
+    <t>48.05866720228968, 1.761736174883102</t>
+  </si>
+  <si>
+    <t>48.056619374316014, 1.766308886649274</t>
   </si>
 </sst>
 </file>
@@ -406,10 +415,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126BFD62-1CFD-4980-84C2-4D9EB355A992}">
-  <dimension ref="B3:N10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:N13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -420,12 +429,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J5" t="s">
         <v>4</v>
       </c>
@@ -434,7 +443,7 @@
         <v>1.13224043715847</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -445,14 +454,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J10" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
